--- a/output/pdf_financials_xlsx/DG.xlsx
+++ b/output/pdf_financials_xlsx/DG.xlsx
@@ -5071,40 +5071,40 @@
         <v>0.317793</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.6367119999999999</v>
+        <v>0.06904399999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.773966</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.804998</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.109307</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.373307</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.373307</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.477307</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.477307</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.477307</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.477307</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.54825</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.54825</v>
       </c>
     </row>
     <row r="93">
@@ -8048,7 +8048,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -8406,7 +8410,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -9594,7 +9602,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DG.xlsx
+++ b/output/pdf_financials_xlsx/DG.xlsx
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.021702</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000855</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>8.3e-05</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>5.1e-05</v>
       </c>
     </row>
     <row r="13">
@@ -1766,7 +1766,7 @@
         <v>-0.8983680000000001</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.021512</v>
+        <v>-1.043214</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.138759</v>
@@ -1775,13 +1775,13 @@
         <v>-0.2849</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.025389</v>
+        <v>-0.026244</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.9419650000000001</v>
+        <v>-0.942048</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.71168</v>
+        <v>-0.711731</v>
       </c>
     </row>
     <row r="28">
@@ -1864,7 +1864,7 @@
         <v>-0.8983680000000001</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.021512</v>
+        <v>-1.043214</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.138759</v>
@@ -1873,13 +1873,13 @@
         <v>-0.2849</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.025389</v>
+        <v>-0.026244</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.9419650000000001</v>
+        <v>-0.942048</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.71168</v>
+        <v>-0.711731</v>
       </c>
     </row>
     <row r="30">
@@ -2117,28 +2117,28 @@
         <v>0.536928</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.681684</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.608285</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.281699</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.739392</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.244875</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.271148</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.410287</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.153021</v>
       </c>
     </row>
     <row r="35">
@@ -2215,28 +2215,28 @@
         <v>0.536928</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.681684</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.608285</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.281699</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.739392</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.244875</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.271148</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.410287</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.153021</v>
       </c>
     </row>
     <row r="37">
@@ -2803,28 +2803,28 @@
         <v>0.087078</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.251113</v>
+        <v>0.569429</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.715535</v>
+        <v>0.10725</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.291699</v>
+        <v>0.01</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.739392</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.261717</v>
+        <v>0.016842</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.285672</v>
+        <v>0.014524</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.415162</v>
+        <v>0.004875</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.155401</v>
+        <v>0.00238</v>
       </c>
     </row>
     <row r="49">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -28116,7 +28116,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">

--- a/output/pdf_financials_xlsx/DG.xlsx
+++ b/output/pdf_financials_xlsx/DG.xlsx
@@ -1199,10 +1199,10 @@
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.111765</v>
+        <v>-0.007722</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0.007722</v>
+        <v>0.007722</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
@@ -1981,7 +1981,7 @@
         <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-15.61107588129632</v>
+        <v>-1.078591043308461</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-1.613985365027809</v>
@@ -5961,10 +5961,10 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.033559</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -6157,13 +6157,13 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.146165</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.138595</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.186489</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -6175,13 +6175,13 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.153516</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.08955100000000001</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.246283</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
@@ -7128,10 +7128,10 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.033559</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.485193</v>
+        <v>-0.491193</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.5471510000000001</v>
+        <v>-0.5807099999999999</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.304924</v>
@@ -14020,7 +14020,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -16610,7 +16614,11 @@
           <t>Proceeds from disposal of marketable securities</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -17894,7 +17902,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -18826,7 +18838,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -18912,7 +18928,11 @@
           <t>Proceeds from the sale of investments</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -19506,7 +19526,11 @@
           <t>Deferred income tax expense (recovery )</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -20626,7 +20650,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -22340,7 +22368,11 @@
           <t>Proceeds from private placement $</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -22510,7 +22542,11 @@
           <t>Proceeds from sale of investments 6 $</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -22938,7 +22974,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -25092,7 +25132,11 @@
           <t>Proceeds from the sale of investments</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -25522,7 +25566,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -31818,7 +31866,11 @@
           <t>Deferred income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -33934,7 +33986,11 @@
           <t>Deferred income tax recovery (expense) 13</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -35990,7 +36046,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
